--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,47 +1009,47 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,51 +1089,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-6.14</v>
+        <v>-8.44</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1227,22 +1227,22 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,22 +1455,22 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1480,27 +1480,27 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,51 +1520,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3.26</v>
+        <v>-6.14</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1613,32 +1613,32 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,27 +1693,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1906,32 +1906,32 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5.85</v>
+        <v>3.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,32 +2044,32 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2089,22 +2089,22 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2134,17 +2134,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>9.52</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,32 +2302,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,51 +2382,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>19.62</v>
+        <v>5.85</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2475,32 +2475,32 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2520,22 +2520,22 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,22 +2778,22 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2813,51 +2813,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1.79</v>
+        <v>19.62</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,27 +2986,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,51 +3244,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
+          <t>4.208403491242825</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>6.05</v>
+        <v>-1.79</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3382,22 +3382,22 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3464,42 +3464,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.29</t>
+          <t>-32.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,37 +3595,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,17 +3635,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.638000000000002</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3675,51 +3675,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.64</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>176.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>167.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5.1624787636147</t>
+          <t>5.298456559293174</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4.3</v>
+        <v>6.05</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.37</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3813,22 +3813,22 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,27 +3848,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,37 +4041,37 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.652000000000001</t>
+          <t>9.638000000000002</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4106,37 +4106,37 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>160.9</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>131.68</t>
+          <t>131.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.883059691404864</t>
+          <t>5.1624787636147</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2.71</v>
+        <v>-4.3</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4244,22 +4244,22 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-33.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,67 +4457,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.684000000000001</t>
+          <t>9.652000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.81</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>155.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>171.9</t>
+          <t>160.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>132.88</t>
+          <t>131.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7.641027506397193</t>
+          <t>6.883059691404864</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>15.64</v>
+        <v>2.71</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4675,22 +4675,22 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4757,127 +4757,127 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-6.34</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-33.56</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>-0.31</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-33.29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,52 +4908,52 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.724</t>
+          <t>9.684000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-23.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,51 +4968,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.30</t>
+          <t>-108.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>171.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>127.76</t>
+          <t>132.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.186912292828493</t>
+          <t>7.641027506397193</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>7.29</v>
+        <v>15.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5106,22 +5106,22 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,27 +5141,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.08</t>
+          <t>-33.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,37 +5334,37 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.742</t>
+          <t>9.724</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.04</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.06</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -5399,51 +5399,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.90</t>
+          <t>-108.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>527.7243125904486</t>
+          <t>527.1806358381504</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>157.6</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>125.76</t>
+          <t>127.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.985696146259683</t>
+          <t>6.186912292828493</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.9</v>
+        <v>7.29</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,17 +5492,17 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>19.2714657415438</t>
+          <t>-4.272042165610985</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-38.41836582380512</t>
+          <t>-24.02392484955233</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-33.833964723614</t>
+          <t>-34.45758219809485</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>57.46%</t>
+          <t>55.36%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>401</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,27 +5572,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-8.44</v>
+        <v>-14.71</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,42 +1309,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,47 +1440,47 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-6.14</v>
+        <v>-8.44</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1911,27 +1911,27 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3.26</v>
+        <v>-6.14</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,17 +2317,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>5.85</v>
+        <v>3.26</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,131 +2733,131 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>9.618</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>9.86</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>9.96</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-7.07</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-110.55</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>526.4978354978355</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>165.6</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>134.46</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>9.626000000000001</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>9.73</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>9.97</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-9.74</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-110.36</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>527.1806358381504</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>427.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>173.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>167.3</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>137.64</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>19.62</v>
+        <v>5.85</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,22 +3209,22 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1.79</v>
+        <v>19.62</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
+          <t>4.208403491242825</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>6.05</v>
+        <v>-1.79</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,42 +3895,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.29</t>
+          <t>-32.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.638000000000002</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.64</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>176.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>167.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5.1624787636147</t>
+          <t>5.298456559293174</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4.3</v>
+        <v>6.05</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.37</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,37 +4472,37 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.652000000000001</t>
+          <t>9.638000000000002</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,27 +4547,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>160.9</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>131.68</t>
+          <t>131.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6.883059691404864</t>
+          <t>5.1624787636147</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2.71</v>
+        <v>-4.3</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-33.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.684000000000001</t>
+          <t>9.652000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-23.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.81</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>155.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>171.9</t>
+          <t>160.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>132.88</t>
+          <t>131.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7.641027506397193</t>
+          <t>6.883059691404864</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>15.64</v>
+        <v>2.71</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,127 +5188,127 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-6.34</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-33.56</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>-0.31</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-33.29</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,52 +5339,52 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.724</t>
+          <t>9.684000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-23.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.30</t>
+          <t>-108.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>527.1806358381504</t>
+          <t>526.4978354978355</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>171.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>127.76</t>
+          <t>132.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.186912292828493</t>
+          <t>7.641027506397193</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>7.29</v>
+        <v>15.64</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>394</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-14.71</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,102 +1334,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-39.21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-33.36</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.87</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-32.11</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1.03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,62 +1445,62 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-8.44</v>
+        <v>-14.71</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,42 +1740,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,126 +1876,126 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>53.85</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>9.642000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>19.90</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-110.19</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>526.0871757925072</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>149.4</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>134.98</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>9.592</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>9.84</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-110.69</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>526.4978354978355</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>147.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>162.2</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>134.36</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-6.14</v>
+        <v>-8.44</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,22 +2317,22 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2342,27 +2342,27 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3.26</v>
+        <v>-6.14</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>5.85</v>
+        <v>3.26</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,27 +3169,27 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>19.62</v>
+        <v>5.85</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,37 +3600,37 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1.79</v>
+        <v>19.62</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,62 +4031,62 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
+          <t>4.208403491242825</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>6.05</v>
+        <v>-1.79</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,42 +4326,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.29</t>
+          <t>-32.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.638000000000002</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.64</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>176.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>167.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5.1624787636147</t>
+          <t>5.298456559293174</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.3</v>
+        <v>6.05</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.37</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.652000000000001</t>
+          <t>9.638000000000002</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>160.9</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>131.68</t>
+          <t>131.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.883059691404864</t>
+          <t>5.1624787636147</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2.71</v>
+        <v>-4.3</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-33.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,62 +5324,62 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.684000000000001</t>
+          <t>9.652000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.39</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.81</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>526.4978354978355</t>
+          <t>526.0871757925072</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>155.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>171.9</t>
+          <t>160.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>132.88</t>
+          <t>131.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7.641027506397193</t>
+          <t>6.883059691404864</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>15.64</v>
+        <v>2.71</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,47 +1014,47 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.72</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-9.359999999999999</v>
+        <v>-15.35</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,67 +1445,67 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-14.71</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,62 +1876,62 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-8.44</v>
+        <v>-14.71</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,42 +2307,42 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-6.14</v>
+        <v>-8.44</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2773,27 +2773,27 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3.26</v>
+        <v>-6.14</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>5.85</v>
+        <v>3.26</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,27 +3600,27 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3630,32 +3630,32 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>19.62</v>
+        <v>5.85</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,37 +4031,37 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4071,22 +4071,22 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1.79</v>
+        <v>19.62</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,62 +4462,62 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
+          <t>4.208403491242825</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>6.05</v>
+        <v>-1.79</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,42 +4757,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.29</t>
+          <t>-32.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,32 +4893,32 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,17 +4928,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.638000000000002</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.64</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>176.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>167.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.1624787636147</t>
+          <t>5.298456559293174</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4.3</v>
+        <v>6.05</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.37</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,37 +5334,37 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.652000000000001</t>
+          <t>9.638000000000002</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>526.0871757925072</t>
+          <t>525.3906474820144</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>160.9</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>131.68</t>
+          <t>131.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.883059691404864</t>
+          <t>5.1624787636147</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2.71</v>
+        <v>-4.3</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>397</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,72 +1014,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>133.72</t>
+          <t>135.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4.661741363888907</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-8.964236188393272</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>164</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-15.28</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-17.38</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,19 +1510,19 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.879469577615386</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-15.35170456411609</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>28</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-17.03</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-14.71</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1.793608670978894</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-9.35695565214455</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>161</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-15.90</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-17.03</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2322,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-0.4184546744033206</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-14.70885164746574</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>36</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-14.32</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-15.90</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,102 +2652,102 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-32.11</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>1.03</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-9.00</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-33.56</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2758,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2793,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-6.14</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>2.179799320698937</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-8.43624408194367</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>101</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-16.16</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-14.32</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>9.54</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3038,7 +3068,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,22 +3209,22 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,27 +3234,27 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>4.10998903027032</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-6.138367413985549</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>46</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>-16.16</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>3.36</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3469,7 +3504,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,17 +3645,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3630,32 +3665,32 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>5.973326565589569</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>3.256398090739793</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>146</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>-16.16</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>3.36</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>9.52</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,32 +4066,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4061,32 +4101,32 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,172 +4156,172 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6.467313561016801</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>5.846906022821003</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>50</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>-16.16</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>3.36</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
           <t>9.6</t>
@@ -4289,7 +4329,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4299,15 +4339,20 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4502,22 +4547,22 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,172 +4592,172 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6.580114931597855</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>19.62452785355052</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>427</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-16.51</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-16.16</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
           <t>9.56</t>
@@ -4720,25 +4765,30 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>4.208403491242825</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1.786888383034096</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>69</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-15.37</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-16.51</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>9.56</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>9.56</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.29</t>
+          <t>-32.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5374,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,17 +5414,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.638000000000002</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,7 +5434,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.64</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>525.3906474820144</t>
+          <t>524.989224137931</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>176.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>167.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.1624787636147</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>5.298456559293174</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>6.046334435524784</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>268</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-15.81</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>224.57</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>9.69</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,59 +1034,59 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>190.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>135.36</t>
+          <t>143.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>164</v>
+        <v>565</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,102 +1344,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-20.20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-34.53</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12.59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.54</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-44.14</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-32.87</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,72 +1450,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>133.72</t>
+          <t>135.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,52 +1886,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1946,19 +1946,19 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.72</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,72 +2322,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,47 +3194,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,22 +3645,22 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3670,27 +3670,27 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3.256398090739793</t>
+          <t>-6.138367413985549</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.846906022821003</t>
+          <t>3.256398090739793</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,32 +4502,32 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4537,32 +4537,32 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19.62452785355052</t>
+          <t>5.846906022821003</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>427</v>
+        <v>50</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,22 +4983,22 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1.786888383034096</t>
+          <t>19.62452785355052</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>69</v>
+        <v>427</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,67 +5374,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.626000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>524.989224137931</t>
+          <t>525.45193687231</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>176.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>167.2</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>131.74</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.298456559293174</t>
+          <t>4.208403491242825</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.046334435524784</t>
+          <t>-1.786888383034096</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>268</v>
+        <v>69</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>190.8</t>
+          <t>306.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>143.74</t>
+          <t>149.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>565</v>
+        <v>614</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,59 +1470,59 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>190.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>135.36</t>
+          <t>143.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>164</v>
+        <v>565</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>133.72</t>
+          <t>135.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,52 +2322,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.72</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,72 +2758,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,67 +3194,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,47 +3630,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,22 +4081,22 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4106,27 +4106,27 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3.256398090739793</t>
+          <t>-6.138367413985549</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4537,32 +4537,32 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.846906022821003</t>
+          <t>3.256398090739793</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,32 +4938,32 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,32 +4973,32 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>19.62452785355052</t>
+          <t>5.846906022821003</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>427</v>
+        <v>50</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,42 +5374,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>525.45193687231</t>
+          <t>526.0186246418339</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>427.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>173.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>131.74</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4.208403491242825</t>
+          <t>6.580114931597855</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1.786888383034096</t>
+          <t>19.62452785355052</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>69</v>
+        <v>427</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>306.4</t>
+          <t>294.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>149.04</t>
+          <t>149.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>614</v>
+        <v>103</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,57 +1465,57 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>190.8</t>
+          <t>306.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>143.74</t>
+          <t>149.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>565</v>
+        <v>614</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,59 +1906,59 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>190.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>135.36</t>
+          <t>143.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>164</v>
+        <v>565</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,72 +2322,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>133.72</t>
+          <t>135.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,52 +2758,52 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2818,19 +2818,19 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.72</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,72 +3194,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,67 +3630,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>134.36</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,22 +4517,22 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4542,27 +4542,27 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>134.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3.256398090739793</t>
+          <t>-6.138367413985549</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,17 +4953,17 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,32 +4973,32 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>134.46</t>
+          <t>134.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.846906022821003</t>
+          <t>3.256398090739793</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,32 +5374,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5409,32 +5409,32 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.626000000000001</t>
+          <t>9.618</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.36</t>
+          <t>-110.55</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>526.0186246418339</t>
+          <t>525.4871244635193</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>137.64</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.580114931597855</t>
+          <t>6.467313561016801</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>19.62452785355052</t>
+          <t>5.846906022821003</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>427</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>9.482000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>9.77</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>103.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>294.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>294.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>196.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>149.22</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>149.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>32.67915614635217</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>103</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>9.498000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>9.78</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9.779999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>614.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>306.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>306.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>191.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>149.04</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>149.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>53.1751787772406</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>614</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>614.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>9.542000000000002</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9.789999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>565.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>190.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>190.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>172.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>143.74</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>143.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>25.80609757932257</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>565</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>9.620000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>9.65</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>164.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>98</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>122.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>135.36</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>135.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-8.964236188393272</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>164</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>9.648000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>28.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>74.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>74.40000000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>133.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>133.72</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>133.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-15.35170456411609</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>28</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>9.628</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>9.67</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>161.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>98</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>133.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-9.35695565214455</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>161</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>9.648000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>9.68</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>9.83</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>36.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>75.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>124.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>132.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>132.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-14.70885164746574</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>36</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>9.642000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>9.84</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>9.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>101.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>154</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>149.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>134.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>134.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-8.43624408194367</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>101</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>9.592</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>9.84</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>9.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>46.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>147.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>147.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>162.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>134.36</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>134.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-6.138367413985549</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>46</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>9.610000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>9.71</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.85</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>192</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>167.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>134.02</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>134.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3.256398090739793</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>146</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>9.618</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>9.72</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>9.86</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>9.859999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>176.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>176</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>165.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>134.46</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>134.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>5.846906022821003</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>50</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,53 +1889,53 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,55 +2324,55 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,51 +3164,51 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN7" t="n">
         <v>9.82</v>
@@ -3220,19 +3220,19 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>75.8</v>
+        <v>98</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>132.3</v>
+        <v>133.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>154</v>
+        <v>75.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>134.98</v>
+        <v>132.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,47 +4454,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>147.6</v>
+        <v>154</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>134.36</v>
+        <v>134.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,22 +4899,22 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,23 +4924,23 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>192</v>
+        <v>147.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>134.02</v>
+        <v>134.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3.256398090739793</t>
+          <t>-6.138367413985549</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>14.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5349,28 +5349,28 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.618</t>
+          <t>9.610000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.55</t>
+          <t>-110.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>525.4871244635193</t>
+          <t>524.8392857142858</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>167.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>134.46</v>
+        <v>134.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.467313561016801</t>
+          <t>5.973326565589569</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.846906022821003</t>
+          <t>3.256398090739793</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,48 +1459,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,53 +2319,53 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,55 +2754,55 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,51 +3594,51 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN8" t="n">
         <v>9.82</v>
@@ -3650,19 +3650,19 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,68 +4024,68 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>75.8</v>
+        <v>98</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>132.3</v>
+        <v>133.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>154</v>
+        <v>75.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>134.98</v>
+        <v>132.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,47 +4884,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>147.6</v>
+        <v>154</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>134.36</v>
+        <v>134.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.70</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,23 +5354,23 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.610000000000001</t>
+          <t>9.592</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.66</t>
+          <t>-110.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>524.8392857142858</t>
+          <t>524.2553495007132</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>192</v>
+        <v>147.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>167.4</t>
+          <t>162.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>134.02</v>
+        <v>134.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.973326565589569</t>
+          <t>4.10998903027032</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3.256398090739793</t>
+          <t>-6.138367413985549</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,48 +1889,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,53 +2749,53 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,55 +3184,55 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,51 +4024,51 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN9" t="n">
         <v>9.82</v>
@@ -4080,19 +4080,19 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>75.8</v>
+        <v>98</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>132.3</v>
+        <v>133.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>154</v>
+        <v>75.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>134.98</v>
+        <v>132.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-32.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,47 +5314,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.592</t>
+          <t>9.642000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.69</t>
+          <t>-110.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>524.2553495007132</t>
+          <t>523.5448717948718</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>147.6</v>
+        <v>154</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>149.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>134.36</v>
+        <v>134.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4.10998903027032</t>
+          <t>2.179799320698937</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6.138367413985549</t>
+          <t>-8.43624408194367</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>388</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,48 +1459,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,48 +2319,48 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,63 +2734,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,53 +3179,53 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,55 +3614,55 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,68 +4024,68 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,51 +4454,51 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN10" t="n">
         <v>9.82</v>
@@ -4510,19 +4510,19 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>75.8</v>
+        <v>98</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>132.3</v>
+        <v>133.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-39.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-33.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.642000000000001</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-109.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>523.5448717948718</t>
+          <t>524.5156472261735</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>154</v>
+        <v>75.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>149.4</t>
+          <t>124.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>134.98</v>
+        <v>132.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2.179799320698937</t>
+          <t>-0.4184546744033206</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8.43624408194367</t>
+          <t>-14.70885164746574</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,48 +1459,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,48 +1889,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,48 +2749,48 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,53 +3609,53 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,55 +4044,55 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,51 +4884,51 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN11" t="n">
         <v>9.82</v>
@@ -4940,19 +4940,19 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.21</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.36</t>
+          <t>-34.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.628</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.74</t>
+          <t>-109.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/17</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>524.5156472261735</t>
+          <t>523.9431818181819</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>75.8</v>
+        <v>98</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>132.3</v>
+        <v>133.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-39</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-0.4184546744033206</t>
+          <t>-1.793608670978894</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-14.70885164746574</t>
+          <t>-9.35695565214455</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-17.03</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,60 +1029,60 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,54 +1444,54 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,48 +1889,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,48 +2319,48 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2734,63 +2734,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,48 +3179,48 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,63 +3594,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,53 +4039,53 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,55 +4474,55 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-44.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-32.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,51 +5314,51 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.628</t>
+          <t>9.648000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AN12" t="n">
         <v>9.82</v>
@@ -5370,19 +5370,19 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.63</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>523.9431818181819</t>
+          <t>523.2276595744681</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>98</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>133.5</v>
+        <v>133.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-39</t>
+          <t>-58</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1.793608670978894</t>
+          <t>-3.879469577615386</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-9.35695565214455</t>
+          <t>-15.35170456411609</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>393</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>3632</t>
@@ -888,7 +884,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +904,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1010,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,32 +1025,28 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.11</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -1065,23 +1057,19 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>29.36</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1189,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,7 +1229,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,22 +1254,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>3632</t>
@@ -1313,12 +1297,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1343,12 +1327,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1407,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1428,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1443,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.23</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
+          <t>70.11</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.51</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.28</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1506,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1607,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,7 +1647,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,17 +1672,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>3632</t>
@@ -1743,12 +1715,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1730,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1815,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1825,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1846,50 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.34</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
+          <t>40.23</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.88</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,18 +1898,14 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.99</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1980,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2025,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2065,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2090,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2137,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2203,12 +2167,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2247,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2268,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,59 +2283,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.25</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-8.93</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-4.99</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2346,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2447,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,7 +2487,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,17 +2512,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2559,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2633,12 +2589,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2669,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2690,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,59 +2705,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.54</t>
-        </is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.39</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.20</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-8.93</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2758,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2768,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2869,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2909,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2934,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +2981,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2996,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3006,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,12 +3091,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,74 +3112,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.54</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.72</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-13.20</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3180,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3190,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3246,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,7 +3301,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3331,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3356,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3493,12 +3433,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3534,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,59 +3549,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.18</t>
-        </is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.61</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.57</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-17.72</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3713,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,7 +3753,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,7 +3778,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,7 +3788,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3840,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3850,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3925,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3956,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-1.18</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.07</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
+          <t>-19.57</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4090,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,7 +4140,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,7 +4175,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4200,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4247,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4262,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4272,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4347,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4357,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4378,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,59 +4393,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.51</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.21</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
+          <t>-19.07</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4446,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4456,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4512,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4557,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,7 +4597,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4622,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4669,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4684,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4694,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4769,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4779,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4800,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4902,56 +4818,48 @@
           <t>21.51</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+      <c r="AH11" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.95</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
+          <t>-12.80</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4868,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4878,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4934,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4979,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +4989,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5019,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5044,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5081,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5091,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5106,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5116,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-44.14</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5191,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-32.87</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5201,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5222,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.84</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
+          <t>21.51</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.648000000000001</t>
+          <t>9.620000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.82</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5290,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5300,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>523.2276595744681</t>
+          <t>522.5672804532578</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>74.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>133.72</v>
+        <v>135.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-58</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.879469577615386</t>
+          <t>-4.661741363888907</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15.35170456411609</t>
+          <t>-8.964236188393272</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5356,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5401,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5411,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5441,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5576,12 +5476,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>3632</t>
@@ -879,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -924,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,12 +993,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1010,50 +1014,50 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1062,11 +1066,11 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.07000000000000001</v>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1194,12 +1198,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1254,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>3632</t>
@@ -1302,7 +1310,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1322,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1342,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1428,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1443,28 +1451,28 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1475,19 +1483,19 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1587,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1607,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>3632</t>
@@ -1715,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1740,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1760,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1825,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1846,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1861,48 +1873,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.08</v>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2005,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2025,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2090,17 +2102,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2127,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2137,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2152,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2162,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2182,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2237,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2247,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2268,50 +2280,50 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2320,14 +2332,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2336,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2346,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2402,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2427,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2447,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2487,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2512,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2559,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2584,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2604,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2669,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2690,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2705,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2758,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2768,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2849,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2869,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2909,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2934,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2981,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3006,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3026,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3112,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3127,44 +3139,44 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ7" t="n">
@@ -3180,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3190,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3271,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3291,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3331,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3356,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3448,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,12 +3525,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3534,59 +3546,59 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.61</v>
+        <v>-1.54</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3693,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3723,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3778,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3870,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3971,44 +3983,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.65</v>
+        <v>-0.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.18</v>
+        <v>-1.61</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4115,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4135,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4175,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4200,7 +4212,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4210,7 +4222,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4247,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.11</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4292,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4347,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.93</v>
+        <v>-0.65</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ10" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4512,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4537,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4597,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4622,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4714,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4815,48 +4827,48 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.95</v>
+        <v>-1.21</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.07000000000000001</v>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4959,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5019,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5044,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5136,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5241,44 +5253,44 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.66</v>
+        <v>-1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.3</v>
+        <v>-0.95</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.620000000000001</t>
+          <t>9.542000000000002</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.07000000000000001</v>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>522.5672804532578</t>
+          <t>521.8748231966053</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>98</v>
+        <v>190.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>135.36</v>
+        <v>143.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4.661741363888907</t>
+          <t>0.02561847352824342</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8.964236188393272</t>
+          <t>25.80609757932257</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5381,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5401,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5411,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5441,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>385</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.07000000000000001</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1436,50 +1436,50 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1488,11 +1488,11 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.07000000000000001</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,28 +1873,28 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,48 +2295,48 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.08</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,50 +2702,50 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,44 +3561,44 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3968,59 +3968,59 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.61</v>
+        <v>-1.54</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,44 +4405,44 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.65</v>
+        <v>-0.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.18</v>
+        <v>-1.61</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.93</v>
+        <v>-0.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ11" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>60.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,48 +5249,48 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.28</v>
+        <v>-0.93</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.95</v>
+        <v>-1.21</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.542000000000002</t>
+          <t>9.498000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.07000000000000001</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>521.8748231966053</t>
+          <t>521.4894067796611</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>190.8</v>
+        <v>306.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>172.4</t>
+          <t>191.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>143.74</v>
+        <v>149.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.02561847352824342</t>
+          <t>8.202473904868608</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>25.80609757932257</t>
+          <t>53.1751787772406</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,44 +1029,44 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,48 +1451,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.07000000000000001</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1863,45 +1863,45 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.07000000000000001</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,28 +2295,28 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -2327,19 +2327,19 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,48 +2717,48 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.08</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,45 +3129,45 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ8" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,44 +3983,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4395,54 +4395,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.61</v>
+        <v>-1.54</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,44 +4827,44 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.65</v>
+        <v>-0.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.18</v>
+        <v>-1.61</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>60.33</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-34.81</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.93</v>
+        <v>-0.65</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.498000000000001</t>
+          <t>9.482000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="AQ12" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>521.4894067796611</t>
+          <t>520.910437235543</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>306.4</v>
+        <v>294.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>191.1</t>
+          <t>196.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.04</v>
+        <v>149.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8.202473904868608</t>
+          <t>11.96811732663531</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>53.1751787772406</t>
+          <t>32.67915614635217</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-17.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1045,32 +1045,32 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.07000000000000001</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,44 +1451,44 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,48 +1873,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.07000000000000001</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2280,50 +2280,50 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2332,11 +2332,11 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.07000000000000001</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,28 +2717,28 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -2749,19 +2749,19 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,48 +3139,48 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.08</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,50 +3546,50 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AQ9" t="n">
         <v>-0.09</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,44 +4405,44 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>48.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.81</t>
+          <t>-34.67</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4812,59 +4812,59 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.61</v>
+        <v>-1.54</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.426000000000002</t>
+          <t>9.422</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.06</t>
+          <t>-111.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>298.8</v>
+        <v>281.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>189.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>144.34</v>
+        <v>144.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>12.18686256885626</t>
+          <t>10.57777233431656</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>13.38996140107147</t>
+          <t>1.72777604434819</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,44 +5249,44 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.65</v>
+        <v>-0.06</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.18</v>
+        <v>-1.61</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.482000000000001</t>
+          <t>9.426000000000002</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ12" t="n">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-111.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>520.910437235543</t>
+          <t>520.1915492957746</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>196.4</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.22</v>
+        <v>144.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>112</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>11.96811732663531</t>
+          <t>12.18686256885626</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>32.67915614635217</t>
+          <t>13.38996140107147</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>251.49</t>
+          <t>252.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -923,162 +923,162 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1094,59 +1094,59 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.28</v>
+        <v>-1.13</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>9.362</t>
+          <t>9.354000000000003</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.24</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>148.56</v>
+        <v>148.4</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-9.23158892994318</t>
+          <t>-12.02586891404593</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-25.67613374474459</t>
+          <t>-27.39440882661108</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-18.17</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,14 +1556,14 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN3" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1575,40 +1575,40 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>9.362</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-109.93</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>61.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>148.7</v>
+        <v>148.56</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,14 +2018,14 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
@@ -2049,32 +2049,32 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0.07000000000000001</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,14 +2480,14 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2495,44 +2495,44 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,14 +2942,14 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2957,48 +2957,48 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0.07000000000000001</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3404,50 +3404,50 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3456,11 +3456,11 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0.07000000000000001</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,14 +3866,14 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -3881,28 +3881,28 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AU8" t="n">
@@ -3913,19 +3913,19 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,14 +4328,14 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN9" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -4343,48 +4343,48 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0.08</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,50 +4790,50 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AU10" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,167 +5081,167 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-18.71</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-34.67</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-5.24</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-34.67</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,14 +5252,14 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
           <t>10.34</t>
@@ -5267,51 +5267,51 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AY11" t="n">
         <v>-0.09</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5693,17 +5693,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,14 +5714,14 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
           <t>10.34</t>
@@ -5729,44 +5729,44 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.54</v>
+        <v>-1.39</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>9.422</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="AY12" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-111.44</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>519.5928270042194</t>
+          <t>518.9262640449438</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>281.4</v>
+        <v>171.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>189.7</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>144.04</v>
+        <v>143.7</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>10.57777233431656</t>
+          <t>7.261353804965267</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>1.72777604434819</t>
+          <t>-10.97894810646682</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>259.36</t>
+          <t>262.28</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>383</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,17 +5958,17 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>0.17</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-1.13</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-1.41</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>9.354000000000003</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>9.77</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-4.82</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-110.24</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>68</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>129.8</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>148.4</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-61</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-12.02586891404593</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-27.39440882661108</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-18.17</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>3.28</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>9.37</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>9.37</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>9.37</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>9.37</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>5.19</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-1.28</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-1.69</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-1.38</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>9.362</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>9.48</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>9.65</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>9.78</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-7.26</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-110.11</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>63.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>128.5</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>148.56</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-62</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-9.23158892994318</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-25.67613374474459</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>63.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-0.88</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-1.35</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>9.412</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>9.5</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>9.66</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>9.79</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-6.30</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-109.93</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>61.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>129.9</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>148.7</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-68</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-6.241671690888379</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-25.84016456548017</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>5.93</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-1.14</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-0.53</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-1.31</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>9.458000000000002</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>9.51</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>9.67</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-2.62</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-109.77</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>62.6</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>150.26</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-71</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-2.678309350053508</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-19.15163128919238</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.53</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-1.62</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-1.68</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-1.26</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>9.504000000000001</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>9.52</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>9.68</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>9.81</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>5.13</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-109.71</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>166.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>64</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>136.9</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>149.6</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-72</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.3168400934262872</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-16.09116834845295</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>166.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>9.34</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-1.18</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-1.23</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>9.522</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>9.69</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>9.82</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>18.30</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-109.83</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>191.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>181.7</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>146.72</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>3.300114355586149</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-21.00153670638048</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-17.82</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>3.29</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>2.96</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>0.76</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-1.7</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-1.21</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>9.528000000000002</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>9.82</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>29.36</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-110.28</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>190.6</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>236.0</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>153.08</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>7.718596366852808</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-11.83772233533475</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-16.16</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>3.36</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>70.11</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.88</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.51</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-1.73</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-1.22</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>9.496</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>9.83</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>19.65</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-111.04</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>198.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>248.6</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>155.56</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-50</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>11.27429067634145</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-0.03806886472176529</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-16.33</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>3.35</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>9.58</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>5.93</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>40.23</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>1.23</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-0.88</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-1.78</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-1.20</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>9.464000000000002</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>9.84</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-111.58</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>81.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>205.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>250.1</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>157.48</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-44</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>13.33108332017113</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>19.49850998132257</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>81.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-16.33</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>3.35</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>9.58</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>9.58</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>9.58</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>9.58</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>62.96</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-5.40</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>10.34</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>10.34</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.08</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-1.82</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-1.18</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>9.431999999999999</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>9.73</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>9.84</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-4.99</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-111.85</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>518.9262640449438</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>804.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>209.8</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>258.1</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>158.84</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>12.2097330181436</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>39.4258186906244</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>804.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-17.55</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>262.28</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>383</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>9.98</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>9.98</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>9.44</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/06/19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>9.426</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-8.93</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>-111.70</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>518.9262640449438</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>181.3</t>
+        </is>
+      </c>
+      <c r="BL12" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>7.261353804965267</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-10.97894810646682</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2025/06/05</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>-17.55</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>-4.272042165610985</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>-24.02392484955233</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>-34.45758219809485</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>55.36%</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>-12.96%</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>262.28</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>研勤-通信網路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>10.34</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>9.426</t>
-        </is>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>-8.93</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-111.70</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>518.9262640449438</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BF12" t="n">
-        <v>171.8</v>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>181.3</t>
-        </is>
-      </c>
-      <c r="BH12" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>7.261353804965267</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>-10.97894810646682</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-17.55</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>-4.272042165610985</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>-24.02392484955233</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-34.45758219809485</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>55.36%</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>-12.96%</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>262.28</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>研勤-通信網路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>9.44</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-35.16</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1134,50 +1134,50 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>9.354000000000003</t>
+          <t>9.364</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.07000000000000001</v>
@@ -1202,53 +1202,53 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-110.24</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>68</v>
+        <v>44.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>148.4</v>
+        <v>147.6</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-61</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-12.02586891404593</t>
+          <t>-14.23917233700077</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-27.39440882661108</t>
+          <t>-26.41234116325236</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,164 +1425,164 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2025/11/21</t>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1616,59 +1616,59 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.28</v>
+        <v>-1.13</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>9.362</t>
+          <t>9.354000000000003</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BC3" t="n">
@@ -1684,53 +1684,53 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.24</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>148.56</v>
+        <v>148.4</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-9.23158892994318</t>
+          <t>-12.02586891404593</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-25.67613374474459</t>
+          <t>-27.39440882661108</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-18.17</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,12 +2098,12 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2117,40 +2117,40 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>9.362</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -2166,53 +2166,53 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-109.93</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>61.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>148.7</v>
+        <v>148.56</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -2611,32 +2611,32 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BD5" t="n">
         <v>-0.07000000000000001</v>
@@ -2648,53 +2648,53 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,44 +3077,44 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="BC6" t="n">
@@ -3130,53 +3130,53 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,48 +3559,48 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD7" t="n">
         <v>-0.07000000000000001</v>
@@ -3612,53 +3612,53 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -4026,50 +4026,50 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -4078,11 +4078,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.07000000000000001</v>
@@ -4094,53 +4094,53 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,28 +4523,28 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -4555,19 +4555,19 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,53 +4576,53 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,48 +5005,48 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.08</v>
@@ -5058,53 +5058,53 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,17 +5234,17 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,50 +5472,50 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AY11" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,53 +5540,53 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,134 +5763,134 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-18.71</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-34.67</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-5.24</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-34.67</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2025/06/19</t>
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.431999999999999</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="BC12" t="n">
         <v>-0.09</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,53 +6022,53 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-111.85</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>518.9262640449438</t>
+          <t>518.3036465638148</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>171.8</v>
+        <v>209.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>258.1</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>143.7</v>
+        <v>158.84</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-48</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>7.261353804965267</t>
+          <t>12.2097330181436</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-10.97894810646682</t>
+          <t>39.4258186906244</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>262.28</t>
+          <t>256.45</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1093,37 +1093,37 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,40 +1153,40 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>9.364</t>
+          <t>9.360000000000001</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>44.8</v>
+        <v>63.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>147.6</v>
+        <v>149.76</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-14.23917233700077</t>
+          <t>-14.56615894204987</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-26.41234116325236</t>
+          <t>-16.36458526981994</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-35.16</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1575,32 +1575,32 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1616,50 +1616,50 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>9.354000000000003</t>
+          <t>9.364</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD3" t="n">
         <v>-0.07000000000000001</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-110.24</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>68</v>
+        <v>44.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>148.4</v>
+        <v>147.6</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-61</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-12.02586891404593</t>
+          <t>-14.23917233700077</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-27.39440882661108</t>
+          <t>-26.41234116325236</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,182 +1907,182 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -2098,59 +2098,59 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.28</v>
+        <v>-1.13</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>9.362</t>
+          <t>9.354000000000003</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.24</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>148.56</v>
+        <v>148.4</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-9.23158892994318</t>
+          <t>-12.02586891404593</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-25.67613374474459</t>
+          <t>-27.39440882661108</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-18.17</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2539,37 +2539,37 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2599,40 +2599,40 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>9.362</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-109.93</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>61.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>148.7</v>
+        <v>148.56</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3021,37 +3021,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -3093,32 +3093,32 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BD6" t="n">
         <v>-0.07000000000000001</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3503,37 +3503,37 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,44 +3559,44 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3985,37 +3985,37 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,48 +4041,48 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.07000000000000001</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4508,50 +4508,50 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.07000000000000001</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4949,37 +4949,37 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,28 +5005,28 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -5037,19 +5037,19 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,37 +5431,37 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,48 +5487,48 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BD11" t="n">
         <v>-0.08</v>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5913,37 +5913,37 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,50 +5954,50 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.08</v>
+        <v>1.23</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.431999999999999</t>
+          <t>9.464000000000002</t>
         </is>
       </c>
       <c r="AY12" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -6006,14 +6006,14 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-111.85</t>
+          <t>-111.58</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>518.3036465638148</t>
+          <t>517.9264705882354</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>209.8</v>
+        <v>205.4</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>258.1</t>
+          <t>250.1</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>158.84</v>
+        <v>157.48</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>12.2097330181436</t>
+          <t>13.33108332017113</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>39.4258186906244</t>
+          <t>19.49850998132257</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>256.45</t>
+          <t>259.84</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>382</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,48 +1149,48 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.86</v>
+        <v>-0.71</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>9.360000000000001</t>
+          <t>9.356</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.07000000000000001</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>63.2</v>
+        <v>84.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>149.76</v>
+        <v>150.04</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-14.56615894204987</t>
+          <t>-14.28629472214555</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-16.36458526981994</t>
+          <t>-12.74704151267176</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,17 +1616,17 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,40 +1635,40 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>9.364</t>
+          <t>9.360000000000001</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="BC3" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>44.8</v>
+        <v>63.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>147.6</v>
+        <v>149.76</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-14.23917233700077</t>
+          <t>-14.56615894204987</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-26.41234116325236</t>
+          <t>-16.36458526981994</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-35.16</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -2098,50 +2098,50 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>9.354000000000003</t>
+          <t>9.364</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD4" t="n">
         <v>-0.07000000000000001</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-110.24</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>68</v>
+        <v>44.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>148.4</v>
+        <v>147.6</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-61</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-12.02586891404593</t>
+          <t>-14.23917233700077</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-27.39440882661108</t>
+          <t>-26.41234116325236</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,182 +2389,182 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2580,59 +2580,59 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.28</v>
+        <v>-1.13</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>9.362</t>
+          <t>9.354000000000003</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>148.56</v>
+        <v>148.4</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-9.23158892994318</t>
+          <t>-12.02586891404593</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-25.67613374474459</t>
+          <t>-27.39440882661108</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-18.17</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,40 +3081,40 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>9.362</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BC6" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-109.93</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>61.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>148.7</v>
+        <v>148.56</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -3575,32 +3575,32 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BD7" t="n">
         <v>-0.07000000000000001</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,44 +4041,44 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="BC8" t="n">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,48 +4523,48 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-1.18</v>
+        <v>-1.62</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9.522</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.07000000000000001</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>191.6</v>
+        <v>64</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>136.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>146.72</v>
+        <v>149.6</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-17.82</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.56</t>
+          <t>-34.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4990,50 +4990,50 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9.528000000000002</t>
+          <t>9.522</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -5042,11 +5042,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.07000000000000001</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-110.28</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>190.6</v>
+        <v>191.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>153.08</v>
+        <v>146.72</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>7.718596366852808</t>
+          <t>3.300114355586149</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11.83772233533475</t>
+          <t>-21.00153670638048</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-17.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,28 +5487,28 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>9.496</t>
+          <t>9.528000000000002</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -5519,19 +5519,19 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>198.4</v>
+        <v>190.6</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>248.6</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>155.56</v>
+        <v>153.08</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-50</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,48 +5969,48 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.464000000000002</t>
+          <t>9.496</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BD12" t="n">
         <v>-0.08</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-111.58</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>517.9264705882354</t>
+          <t>517.4433566433567</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>205.4</v>
+        <v>198.4</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>250.1</t>
+          <t>248.6</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>157.48</v>
+        <v>155.56</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>13.33108332017113</t>
+          <t>11.27429067634145</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>19.49850998132257</t>
+          <t>-0.03806886472176529</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>259.84</t>
+          <t>249.96</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -933,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,470 +948,475 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.73</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-32.66</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-35.43</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>9.432000000000002</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>9.74</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>36.77</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-109.44</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>83</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-14.31472397179257</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-14.47108484485122</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2025/06/05</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>-15.02</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-4.272042165610985</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-24.02392484955233</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>-34.45758219809485</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>55.36%</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>-12.96%</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>253.6</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>研勤-通信網路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>8.89</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>9.356</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>9.74</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-110.31</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>517.4433566433567</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>150.04</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-14.28629472214555</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-12.74704151267176</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-18.52</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>-4.272042165610985</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-24.02392484955233</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-34.45758219809485</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>55.36%</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>-12.96%</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>研勤-通信網路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>9.34</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>9.73</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1425,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,445 +1460,450 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16.01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-35.43</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>8.89</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-35.43</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>9.356</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>9.74</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-110.31</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>150.04</v>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-14.28629472214555</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-12.74704151267176</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2025/06/05</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>-18.52</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>研勤</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-4.272042165610985</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-24.02392484955233</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-34.45758219809485</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>55.36%</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>-12.96%</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>253.6</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>研勤-通信網路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>13.33</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>9.34</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="AT3" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>9.360000000000001</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>9.75</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-110.26</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>517.4433566433567</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>149.76</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-14.56615894204987</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-16.36458526981994</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2025/06/05</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-18.52</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>研勤</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-4.272042165610985</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-24.02392484955233</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-34.45758219809485</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>55.36%</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>-12.96%</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>研勤-通信網路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>9.32</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>9.32</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1897,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,345 +2047,350 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.38</v>
-      </c>
       <c r="AU4" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
+        <v>-0.32</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.86</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>9.364</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.449999999999999</v>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>9.360000000000001</t>
+        </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>9.77</t>
-        </is>
+        <v>9.44</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.609999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.07000000000000001</v>
+          <t>9.75</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
       </c>
       <c r="BD4" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BE4" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-110.23</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>147.6</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>62.9</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>149.76</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-14.23917233700077</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-26.41234116325236</t>
+          <t>-14.56615894204987</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-16.36458526981994</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-17.90</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
+          <t>-18.52</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2379,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-35.16</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2559,300 +2579,305 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.17</v>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
+        <v>0.38</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>9.354000000000003</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.460000000000001</v>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>9.364</t>
+        </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="BA5" t="inlineStr">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>9.77</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-4.82</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.08</v>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
       </c>
       <c r="BD5" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BE5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF5" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-110.24</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>68</v>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>129.8</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
-        <v>148.4</v>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-61</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>147.6</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-12.02586891404593</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-27.39440882661108</t>
+          <t>-14.23917233700077</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>-26.41234116325236</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>-18.17</t>
-        </is>
-      </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>-17.90</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2871,470 +2896,475 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>9.354000000000003</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>9.77</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-4.82</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-110.24</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>68</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>129.8</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-61</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-12.02586891404593</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-27.39440882661108</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>9.362</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>9.78</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-7.26</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-110.11</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>517.4433566433567</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>128.5</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>148.56</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-62</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-9.23158892994318</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-25.67613374474459</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-18.34</t>
-        </is>
-      </c>
       <c r="BU6" t="inlineStr">
         <is>
+          <t>-18.17</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,7 +3388,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3378,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3523,282 +3553,282 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT7" t="n">
-        <v>-0.66</v>
-      </c>
       <c r="AU7" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+        <v>-0.13</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.28</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9.412</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.5</v>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>9.362</t>
+        </is>
       </c>
       <c r="AZ7" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
+        <v>9.48</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.65</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.30</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
+          <t>9.78</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-7.26</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-109.93</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>129.9</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
-        <v>148.7</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-68</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="BM7" t="n">
+        <v>148.56</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3808,15 +3838,20 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3840,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3860,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3960,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,300 +4040,305 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT8" t="n">
-        <v>-1.14</v>
-      </c>
       <c r="AU8" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="AV8" t="inlineStr">
+        <v>-0.66</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.51</v>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>9.412</t>
+        </is>
       </c>
       <c r="AZ8" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
+        <v>9.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.66</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.62</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-6.30</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE8" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BD8" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-109.77</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>150.26</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-71</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>129.9</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
+        <v>148.7</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="CT8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4307,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4342,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4487,282 +4527,282 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>-1.62</v>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
+        <v>-1.14</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.53</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.52</v>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>9.458000000000002</t>
+        </is>
       </c>
       <c r="AZ9" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
+        <v>9.51</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.67</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.07000000000000001</v>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
       </c>
       <c r="BD9" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BE9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-109.71</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>166.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>64</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>136.9</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-72</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>150.26</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>-18.34</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -4772,15 +4812,20 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4799,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-53.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.88</t>
+          <t>-35.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,300 +5014,305 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>-1.18</v>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+        <v>-1.62</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9.522</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.529999999999999</v>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>9.504000000000001</t>
+        </is>
       </c>
       <c r="AZ10" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
+        <v>9.52</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.68</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>18.30</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.06</v>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
       </c>
       <c r="BD10" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BE10" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF10" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-109.83</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>181.7</t>
-        </is>
-      </c>
-      <c r="BL10" t="n">
-        <v>146.72</v>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>64</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>136.9</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
+        <v>149.6</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>3.300114355586149</t>
+          <t>-72</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-21.00153670638048</t>
+          <t>0.3168400934262872</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>-16.09116834845295</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-17.82</t>
-        </is>
-      </c>
       <c r="BU10" t="inlineStr">
         <is>
+          <t>-18.34</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>9.41</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5281,470 +5331,475 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-34.88</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.89</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-19.24</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-33.56</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>9.522</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>9.82</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>18.30</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-109.83</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>191.6</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>181.7</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>146.72</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>3.300114355586149</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-21.00153670638048</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>2.96</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>9.528000000000002</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-110.28</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>517.4433566433567</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
-        <v>153.08</v>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>7.718596366852808</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-11.83772233533475</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-16.16</t>
-        </is>
-      </c>
       <c r="BU11" t="inlineStr">
         <is>
+          <t>-17.82</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5768,7 +5823,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-33.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5933,300 +5988,305 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.88</v>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
+        <v>0.76</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.13</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.496</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>9.528000000000002</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>9.83</t>
-        </is>
-      </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-0.06</v>
+          <t>9.82</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>29.36</t>
+        </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BE12" t="inlineStr">
+        <v>-0.05</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BF12" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-111.04</t>
-        </is>
-      </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>-110.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>517.4433566433567</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>198.4</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>248.6</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
-        <v>155.56</v>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-50</t>
-        </is>
+          <t>516.8337988826815</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>236.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>153.08</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>11.27429067634145</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-0.03806886472176529</t>
+          <t>7.718596366852808</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>-11.83772233533475</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>-16.33</t>
-        </is>
-      </c>
       <c r="BU12" t="inlineStr">
         <is>
+          <t>-16.16</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>研勤</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>-4.272042165610985</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-24.02392484955233</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>-34.45758219809485</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
           <t>55.36%</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>-12.96%</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
-      </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>253.6</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
           <t>掌門精釀啤酒及餐飲24.45%、廣告機22.30%、行車紀錄器及導航機22.14%、人臉辨識專案19.46%、其他11.65% (2024年)</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>研勤-通信網路業-上櫃</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="CU12" t="inlineStr">
+        <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="CU12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 衛星定位系統** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 導航定位** 人工智慧 - 系統整合、電腦視覺** 雲端運算 - 雲端作業系統、SaaS</t>
         </is>
       </c>
-      <c r="CV12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/衛星定位系統.xlsx
+++ b/Result/checksun_type/衛星定位系統.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,32 +1159,32 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.04</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9.432000000000002</t>
+          <t>9.504000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BA2" t="n">
         <v>9.6</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-109.44</t>
+          <t>-108.02</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>83</v>
+        <v>82.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>149.9</v>
+        <v>148.04</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-14.31472397179257</t>
+          <t>-14.7918646001715</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-14.47108484485122</t>
+          <t>-17.41613805625556</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,164 +1435,164 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.73</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-32.66</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>9.33</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-35.43</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2025/12/10</t>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,33 +1631,33 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.28</v>
+        <v>3.16</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.71</v>
+        <v>-0.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1667,11 +1667,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9.356</t>
+          <t>9.432000000000002</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9.42</v>
+        <v>9.44</v>
       </c>
       <c r="BA3" t="n">
         <v>9.6</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="BE3" t="n">
         <v>-0.07000000000000001</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-110.31</t>
+          <t>-109.44</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>84.8</v>
+        <v>83</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>150.04</v>
+        <v>149.9</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-14.28629472214555</t>
+          <t>-14.31472397179257</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-12.74704151267176</t>
+          <t>-14.47108484485122</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-15.02</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,48 +2133,48 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.86</v>
+        <v>-0.71</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9.360000000000001</t>
+          <t>9.356</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BE4" t="n">
         <v>-0.07000000000000001</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-110.31</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>63.2</v>
+        <v>84.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>149.76</v>
+        <v>150.04</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-14.56615894204987</t>
+          <t>-14.28629472214555</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-16.36458526981994</t>
+          <t>-12.74704151267176</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,17 +2605,17 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -2624,40 +2624,40 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9.364</t>
+          <t>9.360000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="BD5" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>44.8</v>
+        <v>63.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>147.6</v>
+        <v>149.76</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-14.23917233700077</t>
+          <t>-14.56615894204987</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-26.41234116325236</t>
+          <t>-16.36458526981994</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-35.16</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3092,50 +3092,50 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9.354000000000003</t>
+          <t>9.364</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE6" t="n">
         <v>-0.07000000000000001</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-110.24</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>68</v>
+        <v>44.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>148.4</v>
+        <v>147.6</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-61</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-12.02586891404593</t>
+          <t>-14.23917233700077</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-27.39440882661108</t>
+          <t>-26.41234116325236</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,174 +3383,174 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-47.61</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2024-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2024-07-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-35.16</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/06/04</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>9.35</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-48.33</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2024-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2024-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2024-07-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-35.29</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/06/04</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>2025-02-26 00:00:00</t>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3579,59 +3579,59 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.28</v>
+        <v>-1.13</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9.362</t>
+          <t>9.354000000000003</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BD7" t="n">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-110.11</t>
+          <t>-110.24</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>148.56</v>
+        <v>148.4</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-62</t>
+          <t>-61</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9.23158892994318</t>
+          <t>-12.02586891404593</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-25.67613374474459</t>
+          <t>-27.39440882661108</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-18.17</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,40 +4085,40 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>9.362</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="BD8" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-109.93</t>
+          <t>-110.11</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>61.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>148.7</v>
+        <v>148.56</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-62</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-6.241671690888379</t>
+          <t>-9.23158892994318</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-25.84016456548017</t>
+          <t>-25.67613374474459</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.14</v>
+        <v>-0.66</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.53</v>
+        <v>-0.88</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4584,32 +4584,32 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9.458000000000002</t>
+          <t>9.412</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BE9" t="n">
         <v>-0.07000000000000001</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-109.77</t>
+          <t>-109.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>150.26</v>
+        <v>148.7</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-71</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2.678309350053508</t>
+          <t>-6.241671690888379</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-19.15163128919238</t>
+          <t>-25.84016456548017</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>257.51</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-53.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,44 +5055,44 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.62</v>
+        <v>-1.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9.504000000000001</t>
+          <t>9.458000000000002</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="BD10" t="n">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-109.71</t>
+          <t>-109.77</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>516.8337988826815</t>
+          <t>516.1673640167364</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>136.9</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>149.6</v>
+        <v>150.26</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-71</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.3168400934262872</t>
+          <t>-2.678309350053508</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-16.09116834845295</t>
+          <t>-19.15163128919238</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="